--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE799592-970B-48E1-B1E1-BB52EDEDD1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0356CFAA-233B-4D9C-A43E-B8C44D98D73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -479,7 +479,7 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  31 July 2026</t>
+    <t xml:space="preserve"> Run Date:  27 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1078,20 +1078,20 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1192,9 +1192,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1694180</xdr:colOff>
+      <xdr:colOff>1697990</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>18051</xdr:rowOff>
+      <xdr:rowOff>21861</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1650,11 +1650,11 @@
     </row>
     <row r="3" spans="1:63" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="107" t="s">
+      <c r="H3" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
       <c r="K3" s="34"/>
       <c r="M3" s="2" t="s">
         <v>38</v>
@@ -2850,11 +2850,11 @@
     </row>
     <row r="3" spans="2:22" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="107" t="s">
+      <c r="H3" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
       <c r="K3" s="34"/>
       <c r="Q3"/>
     </row>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9797215.1999999993</v>
+        <v>9799596.3000000007</v>
       </c>
       <c r="E7" s="16">
-        <v>10406583.199999999</v>
+        <v>10408964.300000001</v>
       </c>
       <c r="F7" s="16">
-        <v>10283338.199999999</v>
+        <v>10285719.300000001</v>
       </c>
       <c r="G7" s="16">
-        <v>10012585.300000001</v>
+        <v>10015085.4</v>
       </c>
       <c r="H7" s="16">
-        <v>9984207.3000000007</v>
+        <v>9986704.6999999993</v>
       </c>
       <c r="I7" s="16">
-        <v>9211646.5</v>
+        <v>9214074.3000000007</v>
       </c>
       <c r="J7" s="16">
-        <v>0</v>
+        <v>9424828.1999999993</v>
       </c>
       <c r="K7" s="16">
         <v>0</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9797215.1999999993</v>
+        <v>9799596.3000000007</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3037,25 +3037,25 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1567050.9</v>
+        <v>1561049.3</v>
       </c>
       <c r="E11" s="16">
-        <v>1445368.3</v>
+        <v>1438634.8</v>
       </c>
       <c r="F11" s="16">
-        <v>1653353.6</v>
+        <v>1642180.9</v>
       </c>
       <c r="G11" s="16">
-        <v>1630395.2</v>
+        <v>1616088.6</v>
       </c>
       <c r="H11" s="16">
-        <v>1647737.4</v>
+        <v>1630926.8</v>
       </c>
       <c r="I11" s="16">
-        <v>1569685.2</v>
+        <v>1555276.7</v>
       </c>
       <c r="J11" s="16">
-        <v>0</v>
+        <v>1616222</v>
       </c>
       <c r="K11" s="16">
         <v>0</v>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>9513590.5999999996</v>
+        <v>11060379.1</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3083,25 +3083,25 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>352073.8</v>
+        <v>354278.1</v>
       </c>
       <c r="E12" s="16">
-        <v>323801.90000000002</v>
+        <v>325771.90000000002</v>
       </c>
       <c r="F12" s="16">
-        <v>357972.1</v>
+        <v>360042.5</v>
       </c>
       <c r="G12" s="16">
-        <v>332830</v>
+        <v>334833.5</v>
       </c>
       <c r="H12" s="16">
-        <v>340149.4</v>
+        <v>343173.9</v>
       </c>
       <c r="I12" s="16">
-        <v>324604.3</v>
+        <v>327072.2</v>
       </c>
       <c r="J12" s="16">
-        <v>0</v>
+        <v>337367.6</v>
       </c>
       <c r="K12" s="16">
         <v>0</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>2031431.4999999998</v>
+        <v>2382539.6999999997</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3128,25 +3128,25 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>175939.4</v>
+        <v>176717</v>
       </c>
       <c r="E13" s="16">
-        <v>156266.29999999999</v>
+        <v>156915.1</v>
       </c>
       <c r="F13" s="16">
-        <v>169881.60000000001</v>
+        <v>170523.1</v>
       </c>
       <c r="G13" s="16">
-        <v>161030.9</v>
+        <v>161484.70000000001</v>
       </c>
       <c r="H13" s="16">
-        <v>158725.4</v>
+        <v>158766.29999999999</v>
       </c>
       <c r="I13" s="16">
-        <v>151327</v>
+        <v>151712.6</v>
       </c>
       <c r="J13" s="16">
-        <v>0</v>
+        <v>157972.4</v>
       </c>
       <c r="K13" s="16">
         <v>0</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>973170.6</v>
+        <v>1134091.2</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3173,25 +3173,25 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>673331.1</v>
+        <v>676586.1</v>
       </c>
       <c r="E14" s="76">
-        <v>615927.9</v>
+        <v>620199.6</v>
       </c>
       <c r="F14" s="76">
-        <v>690537.1</v>
+        <v>699319.9</v>
       </c>
       <c r="G14" s="75">
-        <v>659179.6</v>
+        <v>671388</v>
       </c>
       <c r="H14" s="75">
-        <v>668666.6</v>
+        <v>682683.4</v>
       </c>
       <c r="I14" s="75">
-        <v>650895.4</v>
+        <v>663416.4</v>
       </c>
       <c r="J14" s="75">
-        <v>0</v>
+        <v>690198.5</v>
       </c>
       <c r="K14" s="75">
         <v>0</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>3958537.7</v>
+        <v>4703791.9000000004</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3218,25 +3218,25 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2768395.1999999997</v>
+        <v>2768630.5</v>
       </c>
       <c r="E15" s="16">
-        <v>2541364.4000000004</v>
+        <v>2541521.4000000004</v>
       </c>
       <c r="F15" s="16">
-        <v>2871744.4000000004</v>
+        <v>2872066.4</v>
       </c>
       <c r="G15" s="16">
-        <v>2783435.7</v>
+        <v>2783794.8000000003</v>
       </c>
       <c r="H15" s="16">
-        <v>2815278.8</v>
+        <v>2815550.4</v>
       </c>
       <c r="I15" s="16">
-        <v>2696511.9</v>
+        <v>2697477.9</v>
       </c>
       <c r="J15" s="16">
-        <v>0</v>
+        <v>2801760.5</v>
       </c>
       <c r="K15" s="16">
         <v>0</v>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>16476730.399999999</v>
+        <v>19280801.899999999</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3292,13 +3292,13 @@
         <v>444723.8</v>
       </c>
       <c r="H17" s="16">
-        <v>443731.7</v>
+        <v>443712.9</v>
       </c>
       <c r="I17" s="16">
-        <v>464019.8</v>
+        <v>464110.4</v>
       </c>
       <c r="J17" s="16">
-        <v>0</v>
+        <v>452039</v>
       </c>
       <c r="K17" s="16">
         <v>0</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>2646945.9</v>
+        <v>3099056.7</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3387,19 +3387,19 @@
         <v>9007844</v>
       </c>
       <c r="F21" s="16">
-        <v>9954219.8000000007</v>
+        <v>9954323.4000000004</v>
       </c>
       <c r="G21" s="16">
-        <v>9390632.4000000004</v>
+        <v>9390664.0999999996</v>
       </c>
       <c r="H21" s="16">
-        <v>9149218.3000000007</v>
+        <v>9149229.5999999996</v>
       </c>
       <c r="I21" s="16">
-        <v>9444530.5</v>
+        <v>9444560.1999999993</v>
       </c>
       <c r="J21" s="16">
-        <v>0</v>
+        <v>10279194.9</v>
       </c>
       <c r="K21" s="16">
         <v>0</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>56854995</v>
+        <v>67134366.200000003</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3442,10 +3442,10 @@
         <v>8248260.5999999996</v>
       </c>
       <c r="I22" s="16">
-        <v>8026658.5</v>
+        <v>8026434.5</v>
       </c>
       <c r="J22" s="16">
-        <v>0</v>
+        <v>9300750.1999999993</v>
       </c>
       <c r="K22" s="16">
         <v>0</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>49066784.5</v>
+        <v>58367310.700000003</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3488,10 +3488,10 @@
         <v>-7070611.9000000004</v>
       </c>
       <c r="I23" s="16">
-        <v>-7233292</v>
+        <v>-7233068</v>
       </c>
       <c r="J23" s="16">
-        <v>0</v>
+        <v>-8254196.7000000002</v>
       </c>
       <c r="K23" s="16">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-43607599.200000003</v>
+        <v>-51861571.900000006</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3525,19 +3525,19 @@
         <v>9749859.9000000004</v>
       </c>
       <c r="F24" s="16">
-        <v>10944374.200000001</v>
+        <v>10944477.800000003</v>
       </c>
       <c r="G24" s="16">
-        <v>10078275.300000001</v>
+        <v>10078307</v>
       </c>
       <c r="H24" s="16">
-        <v>10326866.999999998</v>
+        <v>10326878.299999999</v>
       </c>
       <c r="I24" s="16">
-        <v>10237897</v>
+        <v>10237926.699999999</v>
       </c>
       <c r="J24" s="16">
-        <v>0</v>
+        <v>11325748.400000002</v>
       </c>
       <c r="K24" s="16">
         <v>0</v>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>62314180.299999997</v>
+        <v>73640105</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3582,7 +3582,7 @@
         <v>6275595.4000000004</v>
       </c>
       <c r="J25" s="42">
-        <v>0</v>
+        <v>7097904.5999999996</v>
       </c>
       <c r="K25" s="42">
         <v>0</v>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>37482424.399999999</v>
+        <v>44580329</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3615,19 +3615,19 @@
         <v>15525054.800000001</v>
       </c>
       <c r="F26" s="16">
-        <v>17255416.300000001</v>
+        <v>17255519.900000002</v>
       </c>
       <c r="G26" s="16">
-        <v>16563885.700000001</v>
+        <v>16563917.4</v>
       </c>
       <c r="H26" s="16">
-        <v>16420612.599999998</v>
+        <v>16420623.899999999</v>
       </c>
       <c r="I26" s="16">
-        <v>16513492.4</v>
+        <v>16513522.1</v>
       </c>
       <c r="J26" s="16">
-        <v>0</v>
+        <v>18423653</v>
       </c>
       <c r="K26" s="16">
         <v>0</v>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>99796604.699999988</v>
+        <v>118220434</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3672,25 +3672,25 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20759021.399999999</v>
+        <v>20759256.699999999</v>
       </c>
       <c r="E28" s="16">
-        <v>18474479.500000004</v>
+        <v>18474636.500000004</v>
       </c>
       <c r="F28" s="16">
-        <v>20541087.700000003</v>
+        <v>20541513.300000001</v>
       </c>
       <c r="G28" s="16">
-        <v>19792045.200000003</v>
+        <v>19792436</v>
       </c>
       <c r="H28" s="16">
-        <v>19679623.099999998</v>
+        <v>19679887.199999996</v>
       </c>
       <c r="I28" s="16">
-        <v>19674024.100000001</v>
+        <v>19675110.399999999</v>
       </c>
       <c r="J28" s="16">
-        <v>0</v>
+        <v>21677452.5</v>
       </c>
       <c r="K28" s="16">
         <v>0</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>118920281</v>
+        <v>140600292.59999999</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3753,25 +3753,25 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1388572.5</v>
+        <v>1388337.2</v>
       </c>
       <c r="E31" s="16">
-        <v>1223176.8999999999</v>
+        <v>1223019.8999999999</v>
       </c>
       <c r="F31" s="16">
-        <v>1318490.7</v>
+        <v>1318184.1000000001</v>
       </c>
       <c r="G31" s="16">
-        <v>1263815.1000000001</v>
+        <v>1263380.3</v>
       </c>
       <c r="H31" s="16">
-        <v>1251521.7</v>
+        <v>1251140.7</v>
       </c>
       <c r="I31" s="16">
-        <v>1333664.8999999999</v>
+        <v>1334317</v>
       </c>
       <c r="J31" s="16">
-        <v>0</v>
+        <v>1371369.2</v>
       </c>
       <c r="K31" s="16">
         <v>0</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>7779241.7999999989</v>
+        <v>9149748.4000000004</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3816,7 +3816,7 @@
         <v>413013.7</v>
       </c>
       <c r="J32" s="16">
-        <v>0</v>
+        <v>422859.7</v>
       </c>
       <c r="K32" s="16">
         <v>0</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>2281934.2999999998</v>
+        <v>2704794</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3876,10 +3876,10 @@
         <v>10581.2</v>
       </c>
       <c r="I34" s="16">
-        <v>11209</v>
+        <v>10868.1</v>
       </c>
       <c r="J34" s="16">
-        <v>0</v>
+        <v>11580.5</v>
       </c>
       <c r="K34" s="16">
         <v>0</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>66526.7</v>
+        <v>77766.3</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3925,7 +3925,7 @@
         <v>14528.6</v>
       </c>
       <c r="J35" s="16">
-        <v>0</v>
+        <v>10120.1</v>
       </c>
       <c r="K35" s="16">
         <v>0</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>70678.600000000006</v>
+        <v>80798.700000000012</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3965,13 +3965,13 @@
         <v>339859.5</v>
       </c>
       <c r="H36" s="16">
-        <v>380634.4</v>
+        <v>380630.8</v>
       </c>
       <c r="I36" s="16">
-        <v>373853.1</v>
+        <v>372341.4</v>
       </c>
       <c r="J36" s="16">
-        <v>0</v>
+        <v>364230.2</v>
       </c>
       <c r="K36" s="16">
         <v>0</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>2419727.7000000002</v>
+        <v>2782442.6</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4026,16 +4026,16 @@
         <v>295447.3</v>
       </c>
       <c r="G38" s="16">
-        <v>285283.20000000001</v>
+        <v>285340.2</v>
       </c>
       <c r="H38" s="16">
-        <v>217903.3</v>
+        <v>217959.9</v>
       </c>
       <c r="I38" s="16">
         <v>221429.4</v>
       </c>
       <c r="J38" s="16">
-        <v>0</v>
+        <v>269438</v>
       </c>
       <c r="K38" s="16">
         <v>0</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>1570723</v>
+        <v>1840274.5999999999</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4081,7 +4081,7 @@
         <v>32.6</v>
       </c>
       <c r="J39" s="16">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="K39" s="16">
         <v>0</v>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>450.50000000000006</v>
+        <v>478.10000000000008</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4165,7 +4165,7 @@
         <v>481208</v>
       </c>
       <c r="J42" s="78">
-        <v>0</v>
+        <v>389140.4</v>
       </c>
       <c r="K42" s="78">
         <v>0</v>
@@ -4184,8 +4184,7 @@
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
-        <f t="shared" ref="Q42:Q46" si="0">SUM(D42:O42)</f>
-        <v>3064515.4</v>
+        <v>3453655.8</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4194,31 +4193,25 @@
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="78">
-        <f>589852.8+761707.6</f>
         <v>1351560.4</v>
       </c>
       <c r="E43" s="78">
-        <f>532241+732063.8</f>
         <v>1264304.8</v>
       </c>
       <c r="F43" s="78">
-        <f>539759.3+846515.1</f>
         <v>1386274.4</v>
       </c>
       <c r="G43" s="78">
-        <f>536581.6+708570.8</f>
         <v>1245152.3999999999</v>
       </c>
       <c r="H43" s="78">
-        <f>501093.4+653412.8</f>
         <v>1154506.2000000002</v>
       </c>
       <c r="I43" s="78">
-        <f>460702.9+522490.8</f>
         <v>983193.7</v>
       </c>
       <c r="J43" s="78">
-        <v>0</v>
+        <v>1007592.2</v>
       </c>
       <c r="K43" s="78">
         <v>0</v>
@@ -4237,8 +4230,7 @@
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
-        <f t="shared" si="0"/>
-        <v>7384991.9000000004</v>
+        <v>8392584.0999999996</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4262,10 +4254,10 @@
         <v>954781.5</v>
       </c>
       <c r="I44" s="78">
-        <v>804022.8</v>
+        <v>803998.3</v>
       </c>
       <c r="J44" s="78">
-        <v>0</v>
+        <v>846285.9</v>
       </c>
       <c r="K44" s="78">
         <v>0</v>
@@ -4284,8 +4276,7 @@
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
-        <f t="shared" si="0"/>
-        <v>5071835.4999999991</v>
+        <v>5918096.8999999994</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4312,7 +4303,7 @@
         <v>293530.8</v>
       </c>
       <c r="J45" s="80">
-        <v>0</v>
+        <v>359519.9</v>
       </c>
       <c r="K45" s="80">
         <v>0</v>
@@ -4331,8 +4322,7 @@
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
-        <f t="shared" si="0"/>
-        <v>1712328.1000000003</v>
+        <v>2071848.0000000005</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4341,31 +4331,25 @@
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <f t="shared" ref="D46:I46" si="1">SUM(D42:D45)</f>
         <v>3015610.2</v>
       </c>
       <c r="E46" s="89">
-        <f t="shared" si="1"/>
         <v>2756814.4</v>
       </c>
       <c r="F46" s="89">
-        <f t="shared" si="1"/>
         <v>3147803.8</v>
       </c>
       <c r="G46" s="89">
-        <f t="shared" si="1"/>
         <v>2856226.4</v>
       </c>
       <c r="H46" s="89">
-        <f t="shared" si="1"/>
         <v>2895260.8000000003</v>
       </c>
       <c r="I46" s="89">
-        <f t="shared" si="1"/>
-        <v>2561955.2999999998</v>
+        <v>2561930.7999999998</v>
       </c>
       <c r="J46" s="89">
-        <v>0</v>
+        <v>2602538.4</v>
       </c>
       <c r="K46" s="89">
         <v>0</v>
@@ -4384,8 +4368,7 @@
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
-        <f t="shared" si="0"/>
-        <v>17233670.899999999</v>
+        <v>19836184.799999997</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4411,31 +4394,25 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <f t="shared" ref="D48:I48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
-        <v>5604896.2000000011</v>
+        <v>5604660.9000000004</v>
       </c>
       <c r="E48" s="89">
-        <f t="shared" si="2"/>
-        <v>5036736.8</v>
+        <v>5036579.8</v>
       </c>
       <c r="F48" s="89">
-        <f t="shared" si="2"/>
-        <v>5597532.5999999996</v>
+        <v>5597226</v>
       </c>
       <c r="G48" s="89">
-        <f t="shared" si="2"/>
-        <v>5134621.9000000004</v>
+        <v>5134244.0999999996</v>
       </c>
       <c r="H48" s="89">
-        <f t="shared" si="2"/>
-        <v>5119479.4000000004</v>
+        <v>5119151.4000000004</v>
       </c>
       <c r="I48" s="89">
-        <f t="shared" si="2"/>
-        <v>4929686.5999999996</v>
+        <v>4928461.5999999996</v>
       </c>
       <c r="J48" s="89">
-        <v>0</v>
+        <v>5052163.7</v>
       </c>
       <c r="K48" s="89">
         <v>0</v>
@@ -4454,8 +4431,7 @@
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
-        <f>SUM(D48:O48)</f>
-        <v>31422953.5</v>
+        <v>36472487.5</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4498,7 +4474,7 @@
         <v>229881.1</v>
       </c>
       <c r="J50" s="78">
-        <v>0</v>
+        <v>278855</v>
       </c>
       <c r="K50" s="78">
         <v>0</v>
@@ -4517,8 +4493,7 @@
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
-        <f t="shared" ref="Q50:Q52" si="3">SUM(D50:O50)</f>
-        <v>1252366.5</v>
+        <v>1531221.5</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4544,7 +4519,7 @@
         <v>109090</v>
       </c>
       <c r="J51" s="78">
-        <v>0</v>
+        <v>117075.8</v>
       </c>
       <c r="K51" s="78">
         <v>0</v>
@@ -4563,8 +4538,7 @@
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
-        <f t="shared" si="3"/>
-        <v>670587.10000000009</v>
+        <v>787662.90000000014</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4572,25 +4546,25 @@
         <v>17</v>
       </c>
       <c r="D52" s="78">
-        <v>395919.5</v>
+        <v>395870.8</v>
       </c>
       <c r="E52" s="78">
-        <v>351886.4</v>
+        <v>351853.9</v>
       </c>
       <c r="F52" s="78">
-        <v>389952.5</v>
+        <v>389889.1</v>
       </c>
       <c r="G52" s="78">
-        <v>370034.8</v>
+        <v>369944.9</v>
       </c>
       <c r="H52" s="78">
-        <v>370999.9</v>
+        <v>370921.2</v>
       </c>
       <c r="I52" s="78">
-        <v>382034</v>
+        <v>382116</v>
       </c>
       <c r="J52" s="78">
-        <v>0</v>
+        <v>398154.5</v>
       </c>
       <c r="K52" s="78">
         <v>0</v>
@@ -4609,27 +4583,26 @@
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
-        <f t="shared" si="3"/>
-        <v>2260827.1</v>
+        <v>2658750.3999999994</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
       <c r="B53" s="104"/>
       <c r="C53" s="101"/>
-      <c r="D53" s="108"/>
-      <c r="E53" s="108"/>
-      <c r="F53" s="108"/>
-      <c r="G53" s="108"/>
-      <c r="H53" s="108"/>
-      <c r="I53" s="108"/>
-      <c r="J53" s="108"/>
-      <c r="K53" s="108"/>
-      <c r="L53" s="108"/>
-      <c r="M53" s="108"/>
-      <c r="N53" s="108"/>
-      <c r="O53" s="108"/>
-      <c r="P53" s="108"/>
-      <c r="Q53" s="109"/>
+      <c r="D53" s="107"/>
+      <c r="E53" s="107"/>
+      <c r="F53" s="107"/>
+      <c r="G53" s="107"/>
+      <c r="H53" s="107"/>
+      <c r="I53" s="107"/>
+      <c r="J53" s="107"/>
+      <c r="K53" s="107"/>
+      <c r="L53" s="107"/>
+      <c r="M53" s="107"/>
+      <c r="N53" s="107"/>
+      <c r="O53" s="107"/>
+      <c r="P53" s="107"/>
+      <c r="Q53" s="108"/>
     </row>
     <row r="54" spans="2:17" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="B54" s="104" t="s">
@@ -4637,25 +4610,25 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>10407001</v>
+        <v>10409382.1</v>
       </c>
       <c r="E54" s="83">
-        <v>10283387.5</v>
+        <v>10285768.6</v>
       </c>
       <c r="F54" s="83">
-        <v>10012585.300000001</v>
+        <v>10015085.4</v>
       </c>
       <c r="G54" s="83">
-        <v>9984207.3000000007</v>
+        <v>9986704.6999999993</v>
       </c>
       <c r="H54" s="83">
-        <v>9211960.1999999993</v>
+        <v>9214386.5</v>
       </c>
       <c r="I54" s="83">
-        <v>9414910.3000000007</v>
+        <v>9425584.0999999996</v>
       </c>
       <c r="J54" s="83">
-        <v>0</v>
+        <v>9335767.5</v>
       </c>
       <c r="K54" s="83">
         <v>0</v>
@@ -4674,7 +4647,7 @@
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>9414910.3000000007</v>
+        <v>9335767.5</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4691,16 +4664,16 @@
         <v>-18879.5</v>
       </c>
       <c r="G55" s="78">
-        <v>33390.400000000001</v>
+        <v>33374.699999999997</v>
       </c>
       <c r="H55" s="78">
         <v>-39542.699999999997</v>
       </c>
       <c r="I55" s="78">
-        <v>17742.3</v>
+        <v>-3492.3</v>
       </c>
       <c r="J55" s="78">
-        <v>0</v>
+        <v>17704.099999999999</v>
       </c>
       <c r="K55" s="78">
         <v>0</v>
@@ -4719,8 +4692,7 @@
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <f>SUM(D55:O55)</f>
-        <v>43667.100000000006</v>
+        <v>40120.900000000009</v>
       </c>
     </row>
     <row r="56" spans="2:17" ht="15" thickBot="1">
@@ -4746,31 +4718,25 @@
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <f t="shared" ref="D57:I57" si="4">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
-        <v>25094159.5</v>
+        <v>25094208.200000007</v>
       </c>
       <c r="E57" s="89">
-        <f t="shared" si="4"/>
-        <v>22971269.100000005</v>
+        <v>22971301.600000009</v>
       </c>
       <c r="F57" s="89">
-        <f t="shared" si="4"/>
-        <v>25683349.900000002</v>
+        <v>25683413.300000004</v>
       </c>
       <c r="G57" s="89">
-        <f t="shared" si="4"/>
-        <v>24300540.100000001</v>
+        <v>24300630.000000004</v>
       </c>
       <c r="H57" s="89">
-        <f t="shared" si="4"/>
-        <v>24838142.300000001</v>
+        <v>24838228.199999996</v>
       </c>
       <c r="I57" s="89">
-        <f t="shared" si="4"/>
-        <v>23697184.100000001</v>
+        <v>23667482.800000001</v>
       </c>
       <c r="J57" s="89">
-        <v>0</v>
+        <v>26042295.699999999</v>
       </c>
       <c r="K57" s="89">
         <v>0</v>
@@ -4789,8 +4755,7 @@
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <f>SUM(D57:O57)</f>
-        <v>146584645.00000003</v>
+        <v>172597559.80000001</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4815,20 +4780,20 @@
         <v>129</v>
       </c>
       <c r="C59" s="4"/>
-      <c r="D59" s="110"/>
-      <c r="E59" s="110"/>
-      <c r="F59" s="110"/>
-      <c r="G59" s="110"/>
-      <c r="H59" s="110"/>
-      <c r="I59" s="110"/>
-      <c r="J59" s="110"/>
-      <c r="K59" s="110"/>
-      <c r="L59" s="110"/>
-      <c r="M59" s="110"/>
-      <c r="N59" s="110"/>
-      <c r="O59" s="110"/>
-      <c r="P59" s="110"/>
-      <c r="Q59" s="111" t="s">
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="109"/>
+      <c r="J59" s="109"/>
+      <c r="K59" s="109"/>
+      <c r="L59" s="109"/>
+      <c r="M59" s="109"/>
+      <c r="N59" s="109"/>
+      <c r="O59" s="109"/>
+      <c r="P59" s="109"/>
+      <c r="Q59" s="110" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4937,7 +4902,7 @@
         <v>45842.6</v>
       </c>
       <c r="J63" s="90">
-        <v>0</v>
+        <v>21021.5</v>
       </c>
       <c r="K63" s="90">
         <v>0</v>
@@ -4956,8 +4921,7 @@
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <f>SUM(D63:O63)</f>
-        <v>366639.5</v>
+        <v>387661</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4980,10 +4944,10 @@
         <v>2193732.4</v>
       </c>
       <c r="I64" s="90">
-        <v>2529183.4</v>
+        <v>2528988.2999999998</v>
       </c>
       <c r="J64" s="90">
-        <v>0</v>
+        <v>2557577.7999999998</v>
       </c>
       <c r="K64" s="90">
         <v>0</v>
@@ -5002,8 +4966,7 @@
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <f t="shared" ref="Q64:Q70" si="5">SUM(D64:O64)</f>
-        <v>13991362.300000003</v>
+        <v>16548745.000000004</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -5026,10 +4989,10 @@
         <v>14625</v>
       </c>
       <c r="I65" s="90">
-        <v>11975.3</v>
+        <v>12264.5</v>
       </c>
       <c r="J65" s="90">
-        <v>0</v>
+        <v>10856.4</v>
       </c>
       <c r="K65" s="90">
         <v>0</v>
@@ -5048,8 +5011,7 @@
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <f t="shared" si="5"/>
-        <v>66536.800000000003</v>
+        <v>77682.399999999994</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5075,7 +5037,7 @@
         <v>20121</v>
       </c>
       <c r="J66" s="90">
-        <v>0</v>
+        <v>30897.599999999999</v>
       </c>
       <c r="K66" s="90">
         <v>0</v>
@@ -5094,8 +5056,7 @@
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <f t="shared" si="5"/>
-        <v>71969.5</v>
+        <v>102867.1</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5119,10 +5080,10 @@
         <v>0</v>
       </c>
       <c r="I67" s="90">
-        <v>8689.9</v>
+        <v>0</v>
       </c>
       <c r="J67" s="90">
-        <v>0</v>
+        <v>8689.7999999999993</v>
       </c>
       <c r="K67" s="90">
         <v>0</v>
@@ -5141,8 +5102,7 @@
       </c>
       <c r="P67" s="91"/>
       <c r="Q67" s="93">
-        <f t="shared" si="5"/>
-        <v>9660.9</v>
+        <v>9660.7999999999993</v>
       </c>
     </row>
     <row r="68" spans="2:17" s="1" customFormat="1">
@@ -5169,7 +5129,7 @@
         <v>-1177.4000000000001</v>
       </c>
       <c r="J68" s="90">
-        <v>0</v>
+        <v>1064.9000000000001</v>
       </c>
       <c r="K68" s="90">
         <v>0</v>
@@ -5188,8 +5148,7 @@
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <f t="shared" si="5"/>
-        <v>-13520.7</v>
+        <v>-12455.800000000001</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5213,10 +5172,10 @@
         <v>399833.4</v>
       </c>
       <c r="I69" s="90">
-        <v>362394.3</v>
+        <v>362386.6</v>
       </c>
       <c r="J69" s="90">
-        <v>0</v>
+        <v>380471.3</v>
       </c>
       <c r="K69" s="90">
         <v>0</v>
@@ -5235,8 +5194,7 @@
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <f t="shared" si="5"/>
-        <v>2349547.5999999996</v>
+        <v>2730011.1999999997</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5260,10 +5218,10 @@
         <v>2668990.7000000002</v>
       </c>
       <c r="I70" s="90">
-        <v>2977029.0999999996</v>
+        <v>2968425.6</v>
       </c>
       <c r="J70" s="90">
-        <v>0</v>
+        <v>3010579.2999999993</v>
       </c>
       <c r="K70" s="90">
         <v>0</v>
@@ -5282,8 +5240,7 @@
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <f t="shared" si="5"/>
-        <v>16842195.899999999</v>
+        <v>19844171.700000003</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5328,7 +5285,7 @@
         <v>20123902.899999999</v>
       </c>
       <c r="J72" s="78">
-        <v>0</v>
+        <v>22383866.800000001</v>
       </c>
       <c r="K72" s="78">
         <v>0</v>
@@ -5347,8 +5304,7 @@
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <f>SUM(D72:O72)</f>
-        <v>125524988.19999999</v>
+        <v>147908855</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5375,7 +5331,7 @@
         <v>670796.76333333331</v>
       </c>
       <c r="J73" s="78">
-        <v>0</v>
+        <v>722060.21935483871</v>
       </c>
       <c r="K73" s="78">
         <v>0</v>
@@ -5394,8 +5350,7 @@
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <f>AVERAGE(D73:I73)</f>
-        <v>693431.74330261128</v>
+        <v>697521.52559578675</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5422,31 +5377,25 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <f t="shared" ref="D75:I75" si="6">D57-(D70+D72)</f>
-        <v>499020.90000000224</v>
+        <v>499069.60000000894</v>
       </c>
       <c r="E75" s="89">
-        <f t="shared" si="6"/>
-        <v>908327.10000000522</v>
+        <v>908359.60000000894</v>
       </c>
       <c r="F75" s="89">
-        <f t="shared" si="6"/>
-        <v>954613.10000000149</v>
+        <v>954676.50000000373</v>
       </c>
       <c r="G75" s="89">
-        <f t="shared" si="6"/>
-        <v>519695.40000000224</v>
+        <v>519785.30000000447</v>
       </c>
       <c r="H75" s="89">
-        <f t="shared" si="6"/>
-        <v>739552.30000000075</v>
+        <v>739638.19999999553</v>
       </c>
       <c r="I75" s="89">
-        <f t="shared" si="6"/>
-        <v>596252.10000000149</v>
+        <v>575154.30000000075</v>
       </c>
       <c r="J75" s="89">
-        <v>0</v>
+        <v>647849.59999999776</v>
       </c>
       <c r="K75" s="89">
         <v>0</v>
@@ -5465,8 +5414,7 @@
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
-        <f>SUM(D75:O75)</f>
-        <v>4217460.9000000134</v>
+        <v>4844533.1000000201</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5475,31 +5423,25 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <f t="shared" ref="D76:I76" si="7">IF(D57&gt;0,D75/D57,"")</f>
-        <v>1.9885938000832513E-2</v>
+        <v>1.9887840095309674E-2</v>
       </c>
       <c r="E76" s="94">
-        <f t="shared" si="7"/>
-        <v>3.9541877118143422E-2</v>
+        <v>3.9543235982762451E-2</v>
       </c>
       <c r="F76" s="94">
-        <f t="shared" si="7"/>
-        <v>3.716855876343457E-2</v>
+        <v>3.7170935531376723E-2</v>
       </c>
       <c r="G76" s="94">
-        <f t="shared" si="7"/>
-        <v>2.1386166639152281E-2</v>
+        <v>2.13897870137525E-2</v>
       </c>
       <c r="H76" s="94">
-        <f t="shared" si="7"/>
-        <v>2.9774863637849466E-2</v>
+        <v>2.9778219043820352E-2</v>
       </c>
       <c r="I76" s="94">
-        <f t="shared" si="7"/>
-        <v>2.5161305979810547E-2</v>
-      </c>
-      <c r="J76" s="94" t="s">
-        <v>128</v>
+        <v>2.4301456342454834E-2</v>
+      </c>
+      <c r="J76" s="94">
+        <v>2.4876823743307613E-2</v>
       </c>
       <c r="K76" s="94" t="s">
         <v>128</v>
@@ -5518,8 +5460,7 @@
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
-        <f>AVERAGE(D76:I76)</f>
-        <v>2.8819785023203797E-2</v>
+        <v>2.813547110754059E-2</v>
       </c>
     </row>
     <row r="77" spans="2:17" ht="15" thickBot="1">
@@ -5544,32 +5485,26 @@
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D78" s="112">
-        <f t="shared" ref="D78:I78" si="8">(D70+D72)+D75</f>
-        <v>25094159.5</v>
-      </c>
-      <c r="E78" s="112">
-        <f t="shared" si="8"/>
-        <v>22971269.100000005</v>
-      </c>
-      <c r="F78" s="112">
-        <f t="shared" si="8"/>
-        <v>25683349.900000002</v>
-      </c>
-      <c r="G78" s="112">
-        <f t="shared" si="8"/>
-        <v>24300540.100000001</v>
-      </c>
-      <c r="H78" s="112">
-        <f t="shared" si="8"/>
-        <v>24838142.300000001</v>
-      </c>
-      <c r="I78" s="112">
-        <f t="shared" si="8"/>
-        <v>23697184.100000001</v>
+      <c r="D78" s="111">
+        <v>25094208.200000007</v>
+      </c>
+      <c r="E78" s="111">
+        <v>22971301.600000009</v>
+      </c>
+      <c r="F78" s="111">
+        <v>25683413.300000004</v>
+      </c>
+      <c r="G78" s="111">
+        <v>24300630.000000004</v>
+      </c>
+      <c r="H78" s="111">
+        <v>24838228.199999996</v>
+      </c>
+      <c r="I78" s="111">
+        <v>23667482.800000001</v>
       </c>
       <c r="J78" s="106">
-        <v>0</v>
+        <v>26042295.699999999</v>
       </c>
       <c r="K78" s="106">
         <v>0</v>
@@ -5588,8 +5523,7 @@
       </c>
       <c r="P78" s="82"/>
       <c r="Q78" s="82">
-        <f>SUM(D78:O78)</f>
-        <v>146584645.00000003</v>
+        <v>172597559.80000001</v>
       </c>
     </row>
     <row r="79" spans="2:17">
